--- a/output/pdf_financials_xlsx/COSA.xlsx
+++ b/output/pdf_financials_xlsx/COSA.xlsx
@@ -2921,16 +2921,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.487881</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.047149</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.814485</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.898289</v>
       </c>
     </row>
     <row r="93">
@@ -4854,7 +4854,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COSA.xlsx
+++ b/output/pdf_financials_xlsx/COSA.xlsx
@@ -732,13 +732,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.153377</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.203749</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.105474</v>
       </c>
     </row>
     <row r="13">
@@ -1143,13 +1143,13 @@
         <v>-1.13672</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.635023</v>
+        <v>-2.7884</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.247788</v>
+        <v>-6.451537</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.389343</v>
+        <v>-4.494817</v>
       </c>
     </row>
     <row r="28">
@@ -1193,13 +1193,13 @@
         <v>-1.13672</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.633333</v>
+        <v>-2.78671</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.244497</v>
+        <v>-6.448246</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.386061</v>
+        <v>-4.491535</v>
       </c>
     </row>
     <row r="30">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.276036</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.840954</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.276036</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.840954</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.276036</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.176335</v>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">

--- a/output/pdf_financials_xlsx/COSA.xlsx
+++ b/output/pdf_financials_xlsx/COSA.xlsx
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.14126</v>
       </c>
     </row>
     <row r="111">
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01641</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01641</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4141,7 +4141,7 @@
         <v>-0.916838</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.913679</v>
+        <v>-2.930089</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-8.251308999999999</v>
@@ -5862,7 +5862,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -8254,7 +8258,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -10378,7 +10386,11 @@
           <t>Initial public offering shares issued for cash 3,900,000 585,000</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10424,7 +10436,11 @@
           <t>Shares issued for cash 5,600,000 1,400,000</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -10470,7 +10486,11 @@
           <t>Flow-through shares issued for cash 1,714,285 600,000</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
